--- a/Faculdade/Terceiro Semestre/Estatística Aplicada/Correlação e Regressão Linear.xlsx
+++ b/Faculdade/Terceiro Semestre/Estatística Aplicada/Correlação e Regressão Linear.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44334AEB-5F78-48F1-86FA-BCFA5F99E14B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5511E723-4AE6-48F7-99D3-DA802469E02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{DE991BD9-D963-4C6D-9D4C-61E75807FA31}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
   <si>
     <t>X</t>
   </si>
@@ -85,6 +85,48 @@
   </si>
   <si>
     <t>x</t>
+  </si>
+  <si>
+    <t>Módulo</t>
+  </si>
+  <si>
+    <t>Auth</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>DB</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>Cache</t>
+  </si>
+  <si>
+    <t>Reports</t>
+  </si>
+  <si>
+    <t>Complexidade (x)</t>
+  </si>
+  <si>
+    <t>Bugs (y)</t>
+  </si>
+  <si>
+    <t>y        =</t>
+  </si>
+  <si>
+    <t>A.x + B</t>
+  </si>
+  <si>
+    <t>&lt; - - - -</t>
+  </si>
+  <si>
+    <t>Usuários (x)</t>
+  </si>
+  <si>
+    <t>Banda (y)</t>
   </si>
 </sst>
 </file>
@@ -195,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -222,6 +264,12 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -643,7 +691,915 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Complexidade x Bugs</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="pt-BR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Planilha1!$B$22:$B$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Planilha1!$C$22:$C$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6587-48E3-ABC4-FC4AA4E9FCBC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="842263344"/>
+        <c:axId val="842252784"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="842263344"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="842252784"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="842252784"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="842263344"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Usuários x Banda</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="pt-BR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Planilha1!$B$40:$B$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Planilha1!$C$40:$C$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>380</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>490</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>560</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>830</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1290</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1AD6-4ABE-B7B0-C258264D56DC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="847122912"/>
+        <c:axId val="847142592"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="847122912"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="847142592"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="847142592"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="847122912"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1199,6 +2155,1038 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1232,6 +3220,78 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9E983A7-D815-4520-A564-90CCA9CF156A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>288925</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>593725</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFD63862-9924-6F9C-D4F1-0929EDAD4C48}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1557,13 +3617,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9EF3E8D-C1C9-4395-BC37-F13F1CA2B2EC}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1571,7 +3632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C2" s="5">
         <v>100</v>
       </c>
@@ -1579,7 +3640,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C3" s="6">
         <v>200</v>
       </c>
@@ -1587,7 +3648,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C4" s="6">
         <v>300</v>
       </c>
@@ -1595,7 +3656,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C5" s="6">
         <v>400</v>
       </c>
@@ -1603,7 +3664,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C6" s="6">
         <v>500</v>
       </c>
@@ -1611,7 +3672,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C7" s="7">
         <v>600</v>
       </c>
@@ -1619,11 +3680,11 @@
         <v>350</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>2</v>
       </c>
@@ -1635,47 +3696,313 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="G17" t="s">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
         <v>4</v>
       </c>
-      <c r="H17">
+      <c r="C11">
         <f>SLOPE(D2:D7,C2:C7)</f>
         <v>0.6</v>
       </c>
+      <c r="P11" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" t="s">
-        <v>6</v>
-      </c>
-      <c r="G18" t="s">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
         <v>5</v>
       </c>
-      <c r="H18" s="9">
+      <c r="C12" s="9">
         <f>INTERCEPT(D2:D7,C2:C7)</f>
         <v>-33.333333333333343</v>
       </c>
+      <c r="P12">
+        <v>700</v>
+      </c>
+      <c r="Q12">
+        <f>C11*700+C12</f>
+        <v>386.66666666666663</v>
+      </c>
     </row>
-    <row r="19" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C19">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" cm="1">
+        <f t="array" ref="C13:D13">LINEST(D2:D7,C2:C7)</f>
+        <v>0.6</v>
+      </c>
+      <c r="D13">
+        <v>-33.333333333333343</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="1">
+        <v>3</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="1">
+        <v>5</v>
+      </c>
+      <c r="C23" s="1">
+        <v>4</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="1">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1">
+        <v>7</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" cm="1">
+        <f t="array" ref="F24:G24">LINEST(C22:C27,B22:B27)</f>
+        <v>0.93760539629005069</v>
+      </c>
+      <c r="G24">
+        <v>-0.6155143338954483</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="1">
+        <v>10</v>
+      </c>
+      <c r="C25" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="1">
+        <v>12</v>
+      </c>
+      <c r="C26" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="1">
+        <v>15</v>
+      </c>
+      <c r="C27" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E29" s="1">
+        <v>14</v>
+      </c>
+      <c r="F29" s="1">
+        <f>F24 * 14 +G24</f>
+        <v>12.51096121416526</v>
+      </c>
+      <c r="H29" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E30" s="1">
+        <v>18</v>
+      </c>
+      <c r="F30" s="1">
+        <f>F24* 18 +G24</f>
+        <v>16.261382799325464</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A34" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34">
+        <f>CORREL(B22:B27,C22:C27)</f>
+        <v>0.99742856441033245</v>
+      </c>
+      <c r="C34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B40" s="1">
+        <v>50</v>
+      </c>
+      <c r="C40" s="1">
+        <v>110</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" s="1" cm="1">
+        <f t="array" ref="F40:G40">LINEST(C40:C50,B40:B50)</f>
+        <v>2.1330879577198942</v>
+      </c>
+      <c r="G40" s="1">
+        <v>-39.239901849754517</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B41" s="1">
+        <v>80</v>
+      </c>
+      <c r="C41" s="1">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B42" s="1">
+        <v>100</v>
+      </c>
+      <c r="C42" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B43" s="1">
+        <v>150</v>
+      </c>
+      <c r="C43" s="1">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B44" s="1">
+        <v>200</v>
+      </c>
+      <c r="C44" s="1">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B45" s="1">
+        <v>250</v>
+      </c>
+      <c r="C45" s="1">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B46" s="1">
+        <v>300</v>
+      </c>
+      <c r="C46" s="1">
+        <v>560</v>
+      </c>
+      <c r="E46" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B47" s="1">
+        <v>350</v>
+      </c>
+      <c r="C47" s="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B48" s="1">
+        <v>400</v>
+      </c>
+      <c r="C48" s="1">
         <v>700</v>
       </c>
-      <c r="D19">
-        <f>H17*700+H18</f>
-        <v>386.66666666666663</v>
-      </c>
-      <c r="G19" t="s">
-        <v>6</v>
-      </c>
-      <c r="H19" cm="1">
-        <f t="array" ref="H19:I19">LINEST(D2:D7,C2:C7)</f>
-        <v>0.6</v>
-      </c>
-      <c r="I19">
-        <v>-33.333333333333343</v>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B49" s="1">
+        <v>450</v>
+      </c>
+      <c r="C49" s="1">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B50" s="1">
+        <v>500</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A52" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52">
+        <f>CORREL(B40:B50,C40:C50)</f>
+        <v>0.95444869337328408</v>
       </c>
     </row>
   </sheetData>
